--- a/Dataset/3_label/CLOSING_CLOSING_V6_10 divisions_per_second.xlsx
+++ b/Dataset/3_label/CLOSING_CLOSING_V6_10 divisions_per_second.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,6 +972,150 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CLOSING_CLOSING_V6_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>7800</v>
+      </c>
+      <c r="C31" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CLOSING_CLOSING_V6_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C32" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CLOSING_CLOSING_V6_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8200</v>
+      </c>
+      <c r="C33" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CLOSING_CLOSING_V6_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C34" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CLOSING_CLOSING_V6_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>8600</v>
+      </c>
+      <c r="C35" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CLOSING_CLOSING_V6_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>8800</v>
+      </c>
+      <c r="C36" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CLOSING_CLOSING_V6_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C37" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CLOSING_CLOSING_V6_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C38" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
